--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5A0523-4EDE-40E7-9906-096D44ADC8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349447E3-2CCD-44E2-BE88-7D0F9D5D9891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1640,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>3</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F767239B-05BE-48DD-8352-69AE6083ED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5123CCE5-3072-4D38-8F21-9B7A2EB06F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
   <si>
     <t>0:0</t>
   </si>
@@ -644,6 +644,22 @@
   </si>
   <si>
     <t>毫秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>普攻击中目标回复血量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（在用）</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +667,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,7 +762,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -804,6 +820,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -856,7 +878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -913,6 +935,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1197,8 +1222,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F17C44E-7F43-4887-B69D-27FDC1ACC173}">
-  <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultRowHeight="11.25"/>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.5" style="4" customWidth="1"/>
@@ -1217,7 +1242,7 @@
     <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5">
+    <row r="1" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
@@ -1235,7 +1260,7 @@
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="1:14" ht="13.5">
+    <row r="2" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1279,7 +1304,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="13.5">
+    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
@@ -1323,7 +1348,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5">
+    <row r="4" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
         <v>20</v>
       </c>
@@ -1367,7 +1392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5">
+    <row r="5" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A5" s="19">
         <v>550001</v>
       </c>
@@ -1411,7 +1436,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5">
+    <row r="6" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A6" s="19">
         <v>550002</v>
       </c>
@@ -1455,7 +1480,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5">
+    <row r="7" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A7" s="19">
         <v>550003</v>
       </c>
@@ -1497,7 +1522,7 @@
       </c>
       <c r="N7" s="11"/>
     </row>
-    <row r="8" spans="1:14" ht="13.5">
+    <row r="8" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A8" s="19">
         <v>550004</v>
       </c>
@@ -1539,7 +1564,7 @@
       </c>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" ht="13.5">
+    <row r="9" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A9" s="21">
         <v>560001</v>
       </c>
@@ -1583,7 +1608,7 @@
         <v>6000001</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5">
+    <row r="10" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="21">
         <v>560002</v>
       </c>
@@ -1627,7 +1652,7 @@
         <v>6010001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5">
+    <row r="11" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A11" s="10">
         <v>570001</v>
       </c>
@@ -1671,7 +1696,7 @@
         <v>7000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5">
+    <row r="12" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
         <v>570002</v>
       </c>
@@ -1715,7 +1740,7 @@
         <v>7010001</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5">
+    <row r="13" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A13" s="22">
         <v>580001</v>
       </c>
@@ -1759,7 +1784,7 @@
         <v>8000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5">
+    <row r="14" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A14" s="22">
         <v>580002</v>
       </c>
@@ -1803,7 +1828,7 @@
         <v>8010001</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5">
+    <row r="15" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A15" s="23">
         <v>590001</v>
       </c>
@@ -1847,7 +1872,7 @@
         <v>59030001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5">
+    <row r="16" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="23">
         <v>590002</v>
       </c>
@@ -1891,7 +1916,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5">
+    <row r="17" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A17" s="23">
         <v>590003</v>
       </c>
@@ -1933,7 +1958,7 @@
         <v>59090001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5">
+    <row r="18" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A18" s="23">
         <v>590004</v>
       </c>
@@ -1977,7 +2002,7 @@
         <v>54080001</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5">
+    <row r="19" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A19" s="23">
         <v>590005</v>
       </c>
@@ -2021,7 +2046,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5">
+    <row r="20" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A20" s="23">
         <v>590006</v>
       </c>
@@ -2063,7 +2088,7 @@
         <v>9000001</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5">
+    <row r="21" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="24">
         <v>600001</v>
       </c>
@@ -2107,7 +2132,7 @@
         <v>60010001</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5">
+    <row r="22" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A22" s="24">
         <v>600002</v>
       </c>
@@ -2151,7 +2176,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5">
+    <row r="23" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A23" s="24">
         <v>600003</v>
       </c>
@@ -2195,7 +2220,7 @@
         <v>10020001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5">
+    <row r="24" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="25">
         <v>610001</v>
       </c>
@@ -2239,7 +2264,7 @@
         <v>11010001</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5">
+    <row r="25" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="25">
         <v>610002</v>
       </c>
@@ -2283,7 +2308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5">
+    <row r="26" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A26" s="25">
         <v>610003</v>
       </c>
@@ -2327,7 +2352,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5">
+    <row r="27" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A27" s="25">
         <v>610004</v>
       </c>
@@ -2371,7 +2396,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5">
+    <row r="28" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A28" s="25">
         <v>610005</v>
       </c>
@@ -2413,6 +2438,50 @@
       </c>
       <c r="N28" s="25">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A29" s="19">
+        <v>620001</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="20">
+        <v>25</v>
+      </c>
+      <c r="D29" s="19">
+        <v>2</v>
+      </c>
+      <c r="E29" s="26">
+        <v>26010001</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19">
+        <v>100</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19">
+        <v>10000</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19">
+        <v>1</v>
+      </c>
+      <c r="N29" s="19">
+        <v>59260001</v>
       </c>
     </row>
   </sheetData>
@@ -2425,7 +2494,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2AAA09-75EC-48D5-8256-7AA6949156E5}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
@@ -2439,7 +2508,7 @@
     <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
@@ -2447,7 +2516,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2466,7 +2535,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2499,7 +2568,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -2534,7 +2603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>62</v>
       </c>
@@ -2545,7 +2614,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2556,7 +2625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>62</v>
       </c>
@@ -2567,7 +2636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>69</v>
       </c>
@@ -2578,7 +2647,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
@@ -2589,7 +2658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>69</v>
       </c>
@@ -2600,7 +2669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>62</v>
       </c>
@@ -2611,7 +2680,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -2622,7 +2691,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>62</v>
       </c>
@@ -2633,7 +2702,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>62</v>
       </c>
@@ -2644,7 +2713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>62</v>
       </c>
@@ -2655,7 +2724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>69</v>
       </c>
@@ -2666,7 +2735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>69</v>
       </c>
@@ -2677,7 +2746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
@@ -2688,7 +2757,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
@@ -2699,7 +2768,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>85</v>
       </c>
@@ -2710,7 +2779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -2724,7 +2793,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
@@ -2738,7 +2807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>62</v>
       </c>
@@ -2752,62 +2821,62 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E24" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E26" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E27" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E28" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E29" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E30" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E31" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E32" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E33" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="5:5">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E34" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="5:5">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E35" s="1" t="s">
         <v>7</v>
       </c>
@@ -2821,13 +2890,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709BED1B-30AA-4E74-9F53-FE374AA39847}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>161</v>
       </c>
@@ -2838,17 +2907,17 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -2865,7 +2934,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -2877,7 +2946,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="6">
         <v>2</v>
@@ -2887,7 +2956,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -2899,7 +2968,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="6">
         <v>4</v>
@@ -2911,7 +2980,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
@@ -2921,7 +2990,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="6">
         <v>6</v>
@@ -2934,7 +3003,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="6">
         <v>7</v>
@@ -2947,7 +3016,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="6">
         <v>8</v>
@@ -2958,7 +3027,7 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -2969,7 +3038,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <v>10</v>
       </c>
@@ -2981,7 +3050,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -2990,7 +3059,7 @@
       </c>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>12</v>
       </c>
@@ -2999,7 +3068,7 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="6">
         <v>13</v>
       </c>
@@ -3008,7 +3077,7 @@
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -3016,7 +3085,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -3024,7 +3093,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -3035,7 +3104,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="2">
         <v>17</v>
       </c>
